--- a/eda/ket_qua/ket_qua_modelLR.xlsx
+++ b/eda/ket_qua/ket_qua_modelLR.xlsx
@@ -1,37 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ai-project\eda\ket_qua\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230A326C-DF6E-4EC9-87D3-2A2DF27C8B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3360" yWindow="1392" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Validation Accuracy</t>
+  </si>
+  <si>
+    <t>Test Accuracy</t>
+  </si>
+  <si>
+    <t>Mean KFold Accuracy</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>F1-score</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +81,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,106 +405,1776 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Validation Accuracy</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Test Accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mean KFold Accuracy</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>F1-score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37</v>
-      </c>
-      <c r="G2" t="n">
-        <v>132</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B2">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C2">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D2">
+        <v>44</v>
+      </c>
+      <c r="E2">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>37</v>
+      </c>
+      <c r="G2">
+        <v>132</v>
+      </c>
+      <c r="H2">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>0.75</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.7510917030567685</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.7651292802236197</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C3">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" t="n">
-        <v>39</v>
-      </c>
-      <c r="G3" t="n">
-        <v>132</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.583941605839416</v>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>39</v>
+      </c>
+      <c r="G3">
+        <v>132</v>
+      </c>
+      <c r="H3">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B4">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C4">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D4">
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>37</v>
+      </c>
+      <c r="G4">
+        <v>132</v>
+      </c>
+      <c r="H4">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0.75</v>
+      </c>
+      <c r="B5">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C5">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>39</v>
+      </c>
+      <c r="G5">
+        <v>132</v>
+      </c>
+      <c r="H5">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0.78125</v>
+      </c>
+      <c r="B6">
+        <v>0.72052401746724892</v>
+      </c>
+      <c r="C6">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>116</v>
+      </c>
+      <c r="H6">
+        <v>0.60493827160493829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B7">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C7">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>132</v>
+      </c>
+      <c r="H7">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0.75</v>
+      </c>
+      <c r="B8">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C8">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>18</v>
+      </c>
+      <c r="F8">
+        <v>39</v>
+      </c>
+      <c r="G8">
+        <v>132</v>
+      </c>
+      <c r="H8">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0.78125</v>
+      </c>
+      <c r="B9">
+        <v>0.72052401746724892</v>
+      </c>
+      <c r="C9">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D9">
+        <v>49</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>116</v>
+      </c>
+      <c r="H9">
+        <v>0.60493827160493829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B10">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C10">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D10">
+        <v>44</v>
+      </c>
+      <c r="E10">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>37</v>
+      </c>
+      <c r="G10">
+        <v>132</v>
+      </c>
+      <c r="H10">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>0.75</v>
+      </c>
+      <c r="B11">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C11">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>18</v>
+      </c>
+      <c r="F11">
+        <v>39</v>
+      </c>
+      <c r="G11">
+        <v>132</v>
+      </c>
+      <c r="H11">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0.7</v>
+      </c>
+      <c r="B12">
+        <v>0.69432314410480345</v>
+      </c>
+      <c r="C12">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D12">
+        <v>29</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>130</v>
+      </c>
+      <c r="H12">
+        <v>0.453125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B13">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C13">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D13">
+        <v>44</v>
+      </c>
+      <c r="E13">
+        <v>18</v>
+      </c>
+      <c r="F13">
+        <v>37</v>
+      </c>
+      <c r="G13">
+        <v>132</v>
+      </c>
+      <c r="H13">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0.75</v>
+      </c>
+      <c r="B14">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C14">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>39</v>
+      </c>
+      <c r="G14">
+        <v>132</v>
+      </c>
+      <c r="H14">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0.7</v>
+      </c>
+      <c r="B15">
+        <v>0.69432314410480345</v>
+      </c>
+      <c r="C15">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D15">
+        <v>29</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>130</v>
+      </c>
+      <c r="H15">
+        <v>0.453125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B16">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C16">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D16">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>18</v>
+      </c>
+      <c r="F16">
+        <v>37</v>
+      </c>
+      <c r="G16">
+        <v>132</v>
+      </c>
+      <c r="H16">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0.75</v>
+      </c>
+      <c r="B17">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C17">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D17">
+        <v>40</v>
+      </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>39</v>
+      </c>
+      <c r="G17">
+        <v>132</v>
+      </c>
+      <c r="H17">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B18">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C18">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D18">
+        <v>44</v>
+      </c>
+      <c r="E18">
+        <v>18</v>
+      </c>
+      <c r="F18">
+        <v>37</v>
+      </c>
+      <c r="G18">
+        <v>132</v>
+      </c>
+      <c r="H18">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>0.79629629629629628</v>
+      </c>
+      <c r="B19">
+        <v>0.74458874458874458</v>
+      </c>
+      <c r="C19">
+        <v>0.77106918238993705</v>
+      </c>
+      <c r="D19">
+        <v>42</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>39</v>
+      </c>
+      <c r="G19">
+        <v>130</v>
+      </c>
+      <c r="H19">
+        <v>0.58741258741258739</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B20">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C20">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D20">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>18</v>
+      </c>
+      <c r="F20">
+        <v>37</v>
+      </c>
+      <c r="G20">
+        <v>132</v>
+      </c>
+      <c r="H20">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>0.79629629629629628</v>
+      </c>
+      <c r="B21">
+        <v>0.74458874458874458</v>
+      </c>
+      <c r="C21">
+        <v>0.77106918238993705</v>
+      </c>
+      <c r="D21">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>39</v>
+      </c>
+      <c r="G21">
+        <v>130</v>
+      </c>
+      <c r="H21">
+        <v>0.58741258741258739</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B22">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C22">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D22">
+        <v>44</v>
+      </c>
+      <c r="E22">
+        <v>18</v>
+      </c>
+      <c r="F22">
+        <v>37</v>
+      </c>
+      <c r="G22">
+        <v>132</v>
+      </c>
+      <c r="H22">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>0.79629629629629628</v>
+      </c>
+      <c r="B23">
+        <v>0.74458874458874458</v>
+      </c>
+      <c r="C23">
+        <v>0.77106918238993705</v>
+      </c>
+      <c r="D23">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <v>39</v>
+      </c>
+      <c r="G23">
+        <v>130</v>
+      </c>
+      <c r="H23">
+        <v>0.58741258741258739</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C24">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D24">
+        <v>44</v>
+      </c>
+      <c r="E24">
+        <v>18</v>
+      </c>
+      <c r="F24">
+        <v>37</v>
+      </c>
+      <c r="G24">
+        <v>132</v>
+      </c>
+      <c r="H24">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>0.75</v>
+      </c>
+      <c r="B25">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C25">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D25">
+        <v>40</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>132</v>
+      </c>
+      <c r="H25">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B26">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C26">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D26">
+        <v>44</v>
+      </c>
+      <c r="E26">
+        <v>18</v>
+      </c>
+      <c r="F26">
+        <v>37</v>
+      </c>
+      <c r="G26">
+        <v>132</v>
+      </c>
+      <c r="H26">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B27">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C27">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D27">
+        <v>53</v>
+      </c>
+      <c r="E27">
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <v>26</v>
+      </c>
+      <c r="G27">
+        <v>114</v>
+      </c>
+      <c r="H27">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B28">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C28">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D28">
+        <v>44</v>
+      </c>
+      <c r="E28">
+        <v>18</v>
+      </c>
+      <c r="F28">
+        <v>37</v>
+      </c>
+      <c r="G28">
+        <v>132</v>
+      </c>
+      <c r="H28">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0.75</v>
+      </c>
+      <c r="B29">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C29">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D29">
+        <v>40</v>
+      </c>
+      <c r="E29">
+        <v>18</v>
+      </c>
+      <c r="F29">
+        <v>39</v>
+      </c>
+      <c r="G29">
+        <v>132</v>
+      </c>
+      <c r="H29">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B30">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C30">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D30">
+        <v>44</v>
+      </c>
+      <c r="E30">
+        <v>18</v>
+      </c>
+      <c r="F30">
+        <v>37</v>
+      </c>
+      <c r="G30">
+        <v>132</v>
+      </c>
+      <c r="H30">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B31">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C31">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D31">
+        <v>53</v>
+      </c>
+      <c r="E31">
+        <v>36</v>
+      </c>
+      <c r="F31">
+        <v>26</v>
+      </c>
+      <c r="G31">
+        <v>114</v>
+      </c>
+      <c r="H31">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B32">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C32">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D32">
+        <v>44</v>
+      </c>
+      <c r="E32">
+        <v>18</v>
+      </c>
+      <c r="F32">
+        <v>37</v>
+      </c>
+      <c r="G32">
+        <v>132</v>
+      </c>
+      <c r="H32">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B33">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C33">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D33">
+        <v>53</v>
+      </c>
+      <c r="E33">
+        <v>36</v>
+      </c>
+      <c r="F33">
+        <v>26</v>
+      </c>
+      <c r="G33">
+        <v>114</v>
+      </c>
+      <c r="H33">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B34">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C34">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D34">
+        <v>44</v>
+      </c>
+      <c r="E34">
+        <v>18</v>
+      </c>
+      <c r="F34">
+        <v>37</v>
+      </c>
+      <c r="G34">
+        <v>132</v>
+      </c>
+      <c r="H34">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>0.75</v>
+      </c>
+      <c r="B35">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C35">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D35">
+        <v>40</v>
+      </c>
+      <c r="E35">
+        <v>18</v>
+      </c>
+      <c r="F35">
+        <v>39</v>
+      </c>
+      <c r="G35">
+        <v>132</v>
+      </c>
+      <c r="H35">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B36">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C36">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D36">
+        <v>53</v>
+      </c>
+      <c r="E36">
+        <v>36</v>
+      </c>
+      <c r="F36">
+        <v>26</v>
+      </c>
+      <c r="G36">
+        <v>114</v>
+      </c>
+      <c r="H36">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B37">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C37">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D37">
+        <v>44</v>
+      </c>
+      <c r="E37">
+        <v>18</v>
+      </c>
+      <c r="F37">
+        <v>37</v>
+      </c>
+      <c r="G37">
+        <v>132</v>
+      </c>
+      <c r="H37">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>0.75</v>
+      </c>
+      <c r="B38">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C38">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D38">
+        <v>40</v>
+      </c>
+      <c r="E38">
+        <v>18</v>
+      </c>
+      <c r="F38">
+        <v>39</v>
+      </c>
+      <c r="G38">
+        <v>132</v>
+      </c>
+      <c r="H38">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B39">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C39">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D39">
+        <v>53</v>
+      </c>
+      <c r="E39">
+        <v>36</v>
+      </c>
+      <c r="F39">
+        <v>26</v>
+      </c>
+      <c r="G39">
+        <v>114</v>
+      </c>
+      <c r="H39">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B40">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C40">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D40">
+        <v>44</v>
+      </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="F40">
+        <v>37</v>
+      </c>
+      <c r="G40">
+        <v>132</v>
+      </c>
+      <c r="H40">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>0.75</v>
+      </c>
+      <c r="B41">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C41">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D41">
+        <v>40</v>
+      </c>
+      <c r="E41">
+        <v>18</v>
+      </c>
+      <c r="F41">
+        <v>39</v>
+      </c>
+      <c r="G41">
+        <v>132</v>
+      </c>
+      <c r="H41">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B42">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C42">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D42">
+        <v>44</v>
+      </c>
+      <c r="E42">
+        <v>18</v>
+      </c>
+      <c r="F42">
+        <v>37</v>
+      </c>
+      <c r="G42">
+        <v>132</v>
+      </c>
+      <c r="H42">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>0.75</v>
+      </c>
+      <c r="B43">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C43">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D43">
+        <v>40</v>
+      </c>
+      <c r="E43">
+        <v>18</v>
+      </c>
+      <c r="F43">
+        <v>39</v>
+      </c>
+      <c r="G43">
+        <v>132</v>
+      </c>
+      <c r="H43">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B44">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C44">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D44">
+        <v>53</v>
+      </c>
+      <c r="E44">
+        <v>36</v>
+      </c>
+      <c r="F44">
+        <v>26</v>
+      </c>
+      <c r="G44">
+        <v>114</v>
+      </c>
+      <c r="H44">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B45">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C45">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45">
+        <v>18</v>
+      </c>
+      <c r="F45">
+        <v>37</v>
+      </c>
+      <c r="G45">
+        <v>132</v>
+      </c>
+      <c r="H45">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>0.75</v>
+      </c>
+      <c r="B46">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C46">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D46">
+        <v>40</v>
+      </c>
+      <c r="E46">
+        <v>18</v>
+      </c>
+      <c r="F46">
+        <v>39</v>
+      </c>
+      <c r="G46">
+        <v>132</v>
+      </c>
+      <c r="H46">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B47">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C47">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D47">
+        <v>53</v>
+      </c>
+      <c r="E47">
+        <v>36</v>
+      </c>
+      <c r="F47">
+        <v>26</v>
+      </c>
+      <c r="G47">
+        <v>114</v>
+      </c>
+      <c r="H47">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B48">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C48">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D48">
+        <v>44</v>
+      </c>
+      <c r="E48">
+        <v>18</v>
+      </c>
+      <c r="F48">
+        <v>37</v>
+      </c>
+      <c r="G48">
+        <v>132</v>
+      </c>
+      <c r="H48">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>0.75</v>
+      </c>
+      <c r="B49">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C49">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D49">
+        <v>40</v>
+      </c>
+      <c r="E49">
+        <v>18</v>
+      </c>
+      <c r="F49">
+        <v>39</v>
+      </c>
+      <c r="G49">
+        <v>132</v>
+      </c>
+      <c r="H49">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>0.78125</v>
+      </c>
+      <c r="B50">
+        <v>0.72052401746724892</v>
+      </c>
+      <c r="C50">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D50">
+        <v>49</v>
+      </c>
+      <c r="E50">
+        <v>34</v>
+      </c>
+      <c r="F50">
+        <v>30</v>
+      </c>
+      <c r="G50">
+        <v>116</v>
+      </c>
+      <c r="H50">
+        <v>0.60493827160493829</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B51">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C51">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D51">
+        <v>44</v>
+      </c>
+      <c r="E51">
+        <v>18</v>
+      </c>
+      <c r="F51">
+        <v>37</v>
+      </c>
+      <c r="G51">
+        <v>132</v>
+      </c>
+      <c r="H51">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>0.75</v>
+      </c>
+      <c r="B52">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C52">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D52">
+        <v>40</v>
+      </c>
+      <c r="E52">
+        <v>18</v>
+      </c>
+      <c r="F52">
+        <v>39</v>
+      </c>
+      <c r="G52">
+        <v>132</v>
+      </c>
+      <c r="H52">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="B53">
+        <v>0.73799126637554591</v>
+      </c>
+      <c r="C53">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D53">
+        <v>54</v>
+      </c>
+      <c r="E53">
+        <v>35</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+      <c r="G53">
+        <v>115</v>
+      </c>
+      <c r="H53">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B54">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C54">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D54">
+        <v>44</v>
+      </c>
+      <c r="E54">
+        <v>18</v>
+      </c>
+      <c r="F54">
+        <v>37</v>
+      </c>
+      <c r="G54">
+        <v>132</v>
+      </c>
+      <c r="H54">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>0.75</v>
+      </c>
+      <c r="B55">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C55">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D55">
+        <v>40</v>
+      </c>
+      <c r="E55">
+        <v>18</v>
+      </c>
+      <c r="F55">
+        <v>39</v>
+      </c>
+      <c r="G55">
+        <v>132</v>
+      </c>
+      <c r="H55">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B56">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C56">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D56">
+        <v>53</v>
+      </c>
+      <c r="E56">
+        <v>36</v>
+      </c>
+      <c r="F56">
+        <v>26</v>
+      </c>
+      <c r="G56">
+        <v>114</v>
+      </c>
+      <c r="H56">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B57">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C57">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D57">
+        <v>44</v>
+      </c>
+      <c r="E57">
+        <v>18</v>
+      </c>
+      <c r="F57">
+        <v>37</v>
+      </c>
+      <c r="G57">
+        <v>132</v>
+      </c>
+      <c r="H57">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>0.75</v>
+      </c>
+      <c r="B58">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C58">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D58">
+        <v>40</v>
+      </c>
+      <c r="E58">
+        <v>18</v>
+      </c>
+      <c r="F58">
+        <v>39</v>
+      </c>
+      <c r="G58">
+        <v>132</v>
+      </c>
+      <c r="H58">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B59">
+        <v>0.72925764192139741</v>
+      </c>
+      <c r="C59">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D59">
+        <v>53</v>
+      </c>
+      <c r="E59">
+        <v>36</v>
+      </c>
+      <c r="F59">
+        <v>26</v>
+      </c>
+      <c r="G59">
+        <v>114</v>
+      </c>
+      <c r="H59">
+        <v>0.63095238095238093</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B60">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C60">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D60">
+        <v>44</v>
+      </c>
+      <c r="E60">
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <v>37</v>
+      </c>
+      <c r="G60">
+        <v>132</v>
+      </c>
+      <c r="H60">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>0.75</v>
+      </c>
+      <c r="B61">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C61">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D61">
+        <v>40</v>
+      </c>
+      <c r="E61">
+        <v>18</v>
+      </c>
+      <c r="F61">
+        <v>39</v>
+      </c>
+      <c r="G61">
+        <v>132</v>
+      </c>
+      <c r="H61">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="B62">
+        <v>0.73799126637554591</v>
+      </c>
+      <c r="C62">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D62">
+        <v>54</v>
+      </c>
+      <c r="E62">
+        <v>35</v>
+      </c>
+      <c r="F62">
+        <v>25</v>
+      </c>
+      <c r="G62">
+        <v>115</v>
+      </c>
+      <c r="H62">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B63">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C63">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D63">
+        <v>44</v>
+      </c>
+      <c r="E63">
+        <v>18</v>
+      </c>
+      <c r="F63">
+        <v>37</v>
+      </c>
+      <c r="G63">
+        <v>132</v>
+      </c>
+      <c r="H63">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>0.75</v>
+      </c>
+      <c r="B64">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C64">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D64">
+        <v>40</v>
+      </c>
+      <c r="E64">
+        <v>18</v>
+      </c>
+      <c r="F64">
+        <v>39</v>
+      </c>
+      <c r="G64">
+        <v>132</v>
+      </c>
+      <c r="H64">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="B65">
+        <v>0.73799126637554591</v>
+      </c>
+      <c r="C65">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D65">
+        <v>54</v>
+      </c>
+      <c r="E65">
+        <v>35</v>
+      </c>
+      <c r="F65">
+        <v>25</v>
+      </c>
+      <c r="G65">
+        <v>115</v>
+      </c>
+      <c r="H65">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>0.78395061728395066</v>
+      </c>
+      <c r="B66">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="C66">
+        <v>0.77299091544374554</v>
+      </c>
+      <c r="D66">
+        <v>44</v>
+      </c>
+      <c r="E66">
+        <v>18</v>
+      </c>
+      <c r="F66">
+        <v>37</v>
+      </c>
+      <c r="G66">
+        <v>132</v>
+      </c>
+      <c r="H66">
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>0.75</v>
+      </c>
+      <c r="B67">
+        <v>0.75109170305676853</v>
+      </c>
+      <c r="C67">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D67">
+        <v>40</v>
+      </c>
+      <c r="E67">
+        <v>18</v>
+      </c>
+      <c r="F67">
+        <v>39</v>
+      </c>
+      <c r="G67">
+        <v>132</v>
+      </c>
+      <c r="H67">
+        <v>0.58394160583941601</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="B68">
+        <v>0.73799126637554591</v>
+      </c>
+      <c r="C68">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D68">
+        <v>54</v>
+      </c>
+      <c r="E68">
+        <v>35</v>
+      </c>
+      <c r="F68">
+        <v>25</v>
+      </c>
+      <c r="G68">
+        <v>115</v>
+      </c>
+      <c r="H68">
+        <v>0.6428571428571429</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modelLR.xlsx
+++ b/eda/ket_qua/ket_qua_modelLR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,318 @@
         <v>0.6428571428571429</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7729909154437455</v>
+      </c>
+      <c r="D11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>132</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.771069182389937</v>
+      </c>
+      <c r="D12" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G12" t="n">
+        <v>130</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5874125874125874</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.7901234567901234</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7671907756813416</v>
+      </c>
+      <c r="D13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" t="n">
+        <v>118</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6467065868263473</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7729909154437455</v>
+      </c>
+      <c r="D14" t="n">
+        <v>44</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>132</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.771069182389937</v>
+      </c>
+      <c r="D15" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>130</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5874125874125874</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.7901234567901234</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7671907756813416</v>
+      </c>
+      <c r="D16" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27</v>
+      </c>
+      <c r="G16" t="n">
+        <v>118</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6467065868263473</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7729909154437455</v>
+      </c>
+      <c r="D17" t="n">
+        <v>44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>132</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.771069182389937</v>
+      </c>
+      <c r="D18" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>130</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5874125874125874</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.7901234567901234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7671907756813416</v>
+      </c>
+      <c r="D19" t="n">
+        <v>54</v>
+      </c>
+      <c r="E19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27</v>
+      </c>
+      <c r="G19" t="n">
+        <v>118</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6467065868263473</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7729909154437455</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>37</v>
+      </c>
+      <c r="G20" t="n">
+        <v>132</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.7510917030567685</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7651292802236197</v>
+      </c>
+      <c r="D21" t="n">
+        <v>40</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G21" t="n">
+        <v>132</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.583941605839416</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.7379912663755459</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7519916142557651</v>
+      </c>
+      <c r="D22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" t="n">
+        <v>115</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eda/ket_qua/ket_qua_modelLR.xlsx
+++ b/eda/ket_qua/ket_qua_modelLR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,7 +530,7 @@
         <v>0.7379912663755459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7651292802236197</v>
+        <v>0.7519916142557651</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
@@ -623,396 +623,6 @@
         <v>115</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D8" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" t="n">
-        <v>37</v>
-      </c>
-      <c r="G8" t="n">
-        <v>132</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7510917030567685</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7651292802236197</v>
-      </c>
-      <c r="D9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" t="n">
-        <v>39</v>
-      </c>
-      <c r="G9" t="n">
-        <v>132</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.583941605839416</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.7625</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.7379912663755459</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7519916142557651</v>
-      </c>
-      <c r="D10" t="n">
-        <v>54</v>
-      </c>
-      <c r="E10" t="n">
-        <v>35</v>
-      </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G10" t="n">
-        <v>115</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D11" t="n">
-        <v>44</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11" t="n">
-        <v>37</v>
-      </c>
-      <c r="G11" t="n">
-        <v>132</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.7962962962962963</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.771069182389937</v>
-      </c>
-      <c r="D12" t="n">
-        <v>42</v>
-      </c>
-      <c r="E12" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" t="n">
-        <v>39</v>
-      </c>
-      <c r="G12" t="n">
-        <v>130</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5874125874125874</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.7901234567901234</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7671907756813416</v>
-      </c>
-      <c r="D13" t="n">
-        <v>54</v>
-      </c>
-      <c r="E13" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>27</v>
-      </c>
-      <c r="G13" t="n">
-        <v>118</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.6467065868263473</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D14" t="n">
-        <v>44</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" t="n">
-        <v>37</v>
-      </c>
-      <c r="G14" t="n">
-        <v>132</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0.7962962962962963</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.771069182389937</v>
-      </c>
-      <c r="D15" t="n">
-        <v>42</v>
-      </c>
-      <c r="E15" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" t="n">
-        <v>39</v>
-      </c>
-      <c r="G15" t="n">
-        <v>130</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5874125874125874</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0.7901234567901234</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.7671907756813416</v>
-      </c>
-      <c r="D16" t="n">
-        <v>54</v>
-      </c>
-      <c r="E16" t="n">
-        <v>32</v>
-      </c>
-      <c r="F16" t="n">
-        <v>27</v>
-      </c>
-      <c r="G16" t="n">
-        <v>118</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.6467065868263473</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D17" t="n">
-        <v>44</v>
-      </c>
-      <c r="E17" t="n">
-        <v>18</v>
-      </c>
-      <c r="F17" t="n">
-        <v>37</v>
-      </c>
-      <c r="G17" t="n">
-        <v>132</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0.7962962962962963</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.771069182389937</v>
-      </c>
-      <c r="D18" t="n">
-        <v>42</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" t="n">
-        <v>39</v>
-      </c>
-      <c r="G18" t="n">
-        <v>130</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5874125874125874</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.7901234567901234</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.7445887445887446</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7671907756813416</v>
-      </c>
-      <c r="D19" t="n">
-        <v>54</v>
-      </c>
-      <c r="E19" t="n">
-        <v>32</v>
-      </c>
-      <c r="F19" t="n">
-        <v>27</v>
-      </c>
-      <c r="G19" t="n">
-        <v>118</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.6467065868263473</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7729909154437455</v>
-      </c>
-      <c r="D20" t="n">
-        <v>44</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18</v>
-      </c>
-      <c r="F20" t="n">
-        <v>37</v>
-      </c>
-      <c r="G20" t="n">
-        <v>132</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.7510917030567685</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7651292802236197</v>
-      </c>
-      <c r="D21" t="n">
-        <v>40</v>
-      </c>
-      <c r="E21" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" t="n">
-        <v>39</v>
-      </c>
-      <c r="G21" t="n">
-        <v>132</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.583941605839416</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.7625</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.7379912663755459</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7519916142557651</v>
-      </c>
-      <c r="D22" t="n">
-        <v>54</v>
-      </c>
-      <c r="E22" t="n">
-        <v>35</v>
-      </c>
-      <c r="F22" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" t="n">
-        <v>115</v>
-      </c>
-      <c r="H22" t="n">
         <v>0.6428571428571429</v>
       </c>
     </row>
